--- a/templates/LeaveHub_Import_Template.xlsx
+++ b/templates/LeaveHub_Import_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c7506faa4aa11d3/Desktop/LeaveHub/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_A3899ECB5C54ABAD35C7D0C0835FD17E974E3573" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03085A9B-5309-4CC5-802A-56DC67A715E4}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_A3899ECB5C54ABAD35C7D0C0835FD17E974E3573" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{829316A4-6EE6-41E6-BDE1-D88A77F5253C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
   <si>
     <t>LeaveHub — เทมเพลตนำเข้าข้อมูลขึ้น Supabase</t>
   </si>
@@ -172,6 +172,15 @@
   </si>
   <si>
     <t>เหว่าจันทร์</t>
+  </si>
+  <si>
+    <t>leave_paid_business</t>
+  </si>
+  <si>
+    <t>leave_paid_sick</t>
+  </si>
+  <si>
+    <t>leave_matemity</t>
   </si>
 </sst>
 </file>
@@ -719,7 +728,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I501"/>
+  <dimension ref="A1:L501"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -729,11 +738,11 @@
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="8" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>22</v>
       </c>
@@ -756,13 +765,22 @@
         <v>28</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>31</v>
       </c>
@@ -787,11 +805,14 @@
       <c r="H2" s="7">
         <v>30</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>46</v>
       </c>
@@ -810,8 +831,26 @@
       <c r="F3" s="8" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>30</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -819,7 +858,7 @@
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -827,7 +866,7 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -835,7 +874,7 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -843,7 +882,7 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -851,7 +890,7 @@
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -859,7 +898,7 @@
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -867,7 +906,7 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -875,7 +914,7 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -883,7 +922,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -891,7 +930,7 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -899,7 +938,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -907,7 +946,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -4797,7 +4836,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="ตัวเลขไม่ถูกต้อง" error="ต้องเป็นตัวเลขตั้งแต่ 0 ขึ้นไป (ครึ่งวันใช้ 0.5)" sqref="G2:I500" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="ตัวเลขไม่ถูกต้อง" error="ต้องเป็นตัวเลขตั้งแต่ 0 ขึ้นไป (ครึ่งวันใช้ 0.5)" sqref="G2:L500" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/templates/LeaveHub_Import_Template.xlsx
+++ b/templates/LeaveHub_Import_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c7506faa4aa11d3/Desktop/LeaveHub/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_A3899ECB5C54ABAD35C7D0C0835FD17E974E3573" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{829316A4-6EE6-41E6-BDE1-D88A77F5253C}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="11_A3899ECB5C54ABAD35C7D0C0835FD17E974E3573" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79F54A39-0F02-4212-A4AA-AE912B7B5EAE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5700" yWindow="4635" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="อ่านก่อน" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>LeaveHub — เทมเพลตนำเข้าข้อมูลขึ้น Supabase</t>
   </si>
@@ -162,18 +162,6 @@
     <t>รักงาน</t>
   </si>
   <si>
-    <t>00000000001</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>สุริยา</t>
-  </si>
-  <si>
-    <t>เหว่าจันทร์</t>
-  </si>
-  <si>
     <t>leave_paid_business</t>
   </si>
   <si>
@@ -181,6 +169,24 @@
   </si>
   <si>
     <t>leave_matemity</t>
+  </si>
+  <si>
+    <t>68032221</t>
+  </si>
+  <si>
+    <t>TCC</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>Suriya</t>
+  </si>
+  <si>
+    <t>Heoachan</t>
   </si>
 </sst>
 </file>
@@ -303,6 +309,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -728,7 +738,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L501"/>
+  <dimension ref="A1:L500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -765,16 +775,16 @@
         <v>28</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>29</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>30</v>
@@ -814,22 +824,22 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>6</v>
@@ -838,16 +848,16 @@
         <v>6</v>
       </c>
       <c r="I3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -4826,17 +4836,9 @@
       <c r="E500" s="8"/>
       <c r="F500" s="8"/>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A501" s="8"/>
-      <c r="B501" s="8"/>
-      <c r="C501" s="8"/>
-      <c r="D501" s="8"/>
-      <c r="E501" s="8"/>
-      <c r="F501" s="8"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="ตัวเลขไม่ถูกต้อง" error="ต้องเป็นตัวเลขตั้งแต่ 0 ขึ้นไป (ครึ่งวันใช้ 0.5)" sqref="G2:L500" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="ตัวเลขไม่ถูกต้อง" error="ต้องเป็นตัวเลขตั้งแต่ 0 ขึ้นไป (ครึ่งวันใช้ 0.5)" sqref="G2:L499" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/templates/LeaveHub_Import_Template.xlsx
+++ b/templates/LeaveHub_Import_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c7506faa4aa11d3/Desktop/LeaveHub/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="11_A3899ECB5C54ABAD35C7D0C0835FD17E974E3573" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79F54A39-0F02-4212-A4AA-AE912B7B5EAE}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="11_A3899ECB5C54ABAD35C7D0C0835FD17E974E3573" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{086067B4-25BB-4B61-9E34-318B07D21C31}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="4635" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="อ่านก่อน" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
   <si>
     <t>LeaveHub — เทมเพลตนำเข้าข้อมูลขึ้น Supabase</t>
   </si>
@@ -171,22 +171,43 @@
     <t>leave_matemity</t>
   </si>
   <si>
-    <t>68032221</t>
-  </si>
-  <si>
-    <t>TCC</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
     <t>Mr.</t>
   </si>
   <si>
-    <t>Suriya</t>
+    <t>SNIC001</t>
   </si>
   <si>
-    <t>Heoachan</t>
+    <t>STT001</t>
+  </si>
+  <si>
+    <t>Ms.</t>
+  </si>
+  <si>
+    <t>Noppadol</t>
+  </si>
+  <si>
+    <t>Limjaroen</t>
+  </si>
+  <si>
+    <t>Rodcharin</t>
+  </si>
+  <si>
+    <t>Seekamfong</t>
+  </si>
+  <si>
+    <t>NIC</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>NIC00001</t>
+  </si>
+  <si>
+    <t>TT00001</t>
+  </si>
+  <si>
+    <t>NULL</t>
   </si>
 </sst>
 </file>
@@ -309,10 +330,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -823,42 +840,12 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>6</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>6</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
@@ -4914,43 +4901,61 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
+      <c r="A3" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
+      <c r="A4" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -9905,7 +9910,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" errorTitle="role ไม่ถูกต้อง" error="เลือกได้เฉพาะ admin หรือ supervisor" sqref="C2:C500" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="role ไม่ถูกต้อง" error="เลือกได้เฉพาะ admin หรือ supervisor" sqref="C2:C4 C7:C500" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"admin,supervisor"</formula1>
     </dataValidation>
   </dataValidations>

--- a/templates/LeaveHub_Import_Template.xlsx
+++ b/templates/LeaveHub_Import_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c7506faa4aa11d3/Desktop/LeaveHub/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="11_A3899ECB5C54ABAD35C7D0C0835FD17E974E3573" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{086067B4-25BB-4B61-9E34-318B07D21C31}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="11_A3899ECB5C54ABAD35C7D0C0835FD17E974E3573" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7621322-04F7-408F-A9D4-EBFA27498D7A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="อ่านก่อน" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
   <si>
     <t>LeaveHub — เทมเพลตนำเข้าข้อมูลขึ้น Supabase</t>
   </si>
@@ -170,45 +170,6 @@
   <si>
     <t>leave_matemity</t>
   </si>
-  <si>
-    <t>Mr.</t>
-  </si>
-  <si>
-    <t>SNIC001</t>
-  </si>
-  <si>
-    <t>STT001</t>
-  </si>
-  <si>
-    <t>Ms.</t>
-  </si>
-  <si>
-    <t>Noppadol</t>
-  </si>
-  <si>
-    <t>Limjaroen</t>
-  </si>
-  <si>
-    <t>Rodcharin</t>
-  </si>
-  <si>
-    <t>Seekamfong</t>
-  </si>
-  <si>
-    <t>NIC</t>
-  </si>
-  <si>
-    <t>TT</t>
-  </si>
-  <si>
-    <t>NIC00001</t>
-  </si>
-  <si>
-    <t>TT00001</t>
-  </si>
-  <si>
-    <t>NULL</t>
-  </si>
 </sst>
 </file>
 
@@ -330,6 +291,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4901,56 +4866,22 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>61</v>
-      </c>
+      <c r="A3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>61</v>
-      </c>
+      <c r="A4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H5" s="8"/>
